--- a/research/traditional_assets/database/data/oman/oman_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_brokerage_investment_banking.xlsx
@@ -588,10 +588,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.381</v>
-      </c>
-      <c r="E2">
-        <v>-0.0864</v>
+        <v>0.0323</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,82 +603,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>3.11</v>
+        <v>-0.062</v>
       </c>
       <c r="L2">
-        <v>0.07440191387559809</v>
+        <v>-0.001648936170212766</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.1325342465753425</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-62.41935483870968</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.1325342465753425</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-62.41935483870968</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>18.8</v>
+        <v>22.5</v>
       </c>
       <c r="V2">
-        <v>0.5749235474006116</v>
+        <v>0.7705479452054794</v>
       </c>
       <c r="W2">
-        <v>0.0424863387978142</v>
+        <v>-0.0007969151670951157</v>
       </c>
       <c r="X2">
-        <v>0.06085135079799826</v>
+        <v>0.1136065211799718</v>
       </c>
       <c r="Y2">
-        <v>-0.01836501200018405</v>
+        <v>-0.114403436347067</v>
       </c>
       <c r="Z2">
-        <v>0.4899777282850779</v>
+        <v>0.5236768802228413</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05847176707304773</v>
+        <v>0.1059239785773406</v>
       </c>
       <c r="AC2">
-        <v>-0.05847176707304773</v>
+        <v>-0.1059239785773406</v>
       </c>
       <c r="AD2">
-        <v>12.8</v>
+        <v>12.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>12.8</v>
+        <v>12.1</v>
       </c>
       <c r="AG2">
-        <v>-6</v>
+        <v>-10.4</v>
       </c>
       <c r="AH2">
-        <v>0.2813186813186813</v>
+        <v>0.2929782082324455</v>
       </c>
       <c r="AI2">
-        <v>0.1060480530240265</v>
+        <v>0.1006655574043261</v>
       </c>
       <c r="AJ2">
-        <v>-0.2247191011235955</v>
+        <v>-0.5531914893617023</v>
       </c>
       <c r="AK2">
-        <v>-0.05888125613346418</v>
+        <v>-0.1064483111566019</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -707,10 +707,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.381</v>
-      </c>
-      <c r="E3">
-        <v>-0.0864</v>
+        <v>0.0323</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,82 +722,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3.11</v>
+        <v>-0.062</v>
       </c>
       <c r="L3">
-        <v>0.07440191387559809</v>
+        <v>-0.001648936170212766</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>3.87</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.1325342465753425</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>-62.41935483870968</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>3.87</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.1325342465753425</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>-62.41935483870968</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>18.8</v>
+        <v>22.5</v>
       </c>
       <c r="V3">
-        <v>0.5749235474006116</v>
+        <v>0.7705479452054794</v>
       </c>
       <c r="W3">
-        <v>0.0424863387978142</v>
+        <v>-0.0007969151670951157</v>
       </c>
       <c r="X3">
-        <v>0.06085135079799826</v>
+        <v>0.1136065211799718</v>
       </c>
       <c r="Y3">
-        <v>-0.01836501200018405</v>
+        <v>-0.114403436347067</v>
       </c>
       <c r="Z3">
-        <v>0.4899777282850779</v>
+        <v>0.5236768802228413</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05847176707304773</v>
+        <v>0.1059239785773406</v>
       </c>
       <c r="AC3">
-        <v>-0.05847176707304773</v>
+        <v>-0.1059239785773406</v>
       </c>
       <c r="AD3">
-        <v>12.8</v>
+        <v>12.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>12.8</v>
+        <v>12.1</v>
       </c>
       <c r="AG3">
-        <v>-6</v>
+        <v>-10.4</v>
       </c>
       <c r="AH3">
-        <v>0.2813186813186813</v>
+        <v>0.2929782082324455</v>
       </c>
       <c r="AI3">
-        <v>0.1060480530240265</v>
+        <v>0.1006655574043261</v>
       </c>
       <c r="AJ3">
-        <v>-0.2247191011235955</v>
+        <v>-0.5531914893617023</v>
       </c>
       <c r="AK3">
-        <v>-0.05888125613346418</v>
+        <v>-0.1064483111566019</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/oman/oman_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_brokerage_investment_banking.xlsx
@@ -588,7 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0323</v>
+        <v>0.048</v>
+      </c>
+      <c r="E2">
+        <v>0.399</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,85 +606,82 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>-0.062</v>
+        <v>3.23</v>
       </c>
       <c r="L2">
-        <v>-0.001648936170212766</v>
+        <v>0.06632443531827514</v>
       </c>
       <c r="M2">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.1325342465753425</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-62.41935483870968</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.1325342465753425</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-62.41935483870968</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>22.5</v>
+        <v>26.8</v>
       </c>
       <c r="V2">
-        <v>0.7705479452054794</v>
+        <v>0.8454258675078865</v>
       </c>
       <c r="W2">
-        <v>-0.0007969151670951157</v>
+        <v>0.04162371134020619</v>
       </c>
       <c r="X2">
-        <v>0.1136065211799718</v>
+        <v>0.08021596592832611</v>
       </c>
       <c r="Y2">
-        <v>-0.114403436347067</v>
+        <v>-0.03859225458811992</v>
       </c>
       <c r="Z2">
-        <v>0.5236768802228413</v>
+        <v>0.7247023809523812</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1059239785773406</v>
+        <v>0.07724362736925268</v>
       </c>
       <c r="AC2">
-        <v>-0.1059239785773406</v>
+        <v>-0.07724362736925268</v>
       </c>
       <c r="AD2">
-        <v>12.1</v>
+        <v>11</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>12.1</v>
+        <v>11</v>
       </c>
       <c r="AG2">
-        <v>-10.4</v>
+        <v>-15.8</v>
       </c>
       <c r="AH2">
-        <v>0.2929782082324455</v>
+        <v>0.2576112412177986</v>
       </c>
       <c r="AI2">
-        <v>0.1006655574043261</v>
+        <v>0.08613938919342208</v>
       </c>
       <c r="AJ2">
-        <v>-0.5531914893617023</v>
+        <v>-0.9937106918238995</v>
       </c>
       <c r="AK2">
-        <v>-0.1064483111566019</v>
+        <v>-0.1565906838453915</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -707,7 +707,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0323</v>
+        <v>0.048</v>
+      </c>
+      <c r="E3">
+        <v>0.399</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -722,85 +725,82 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>-0.062</v>
+        <v>3.23</v>
       </c>
       <c r="L3">
-        <v>-0.001648936170212766</v>
+        <v>0.06632443531827514</v>
       </c>
       <c r="M3">
-        <v>3.87</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.1325342465753425</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-62.41935483870968</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>3.87</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.1325342465753425</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-62.41935483870968</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>22.5</v>
+        <v>26.8</v>
       </c>
       <c r="V3">
-        <v>0.7705479452054794</v>
+        <v>0.8454258675078865</v>
       </c>
       <c r="W3">
-        <v>-0.0007969151670951157</v>
+        <v>0.04162371134020619</v>
       </c>
       <c r="X3">
-        <v>0.1136065211799718</v>
+        <v>0.08021596592832611</v>
       </c>
       <c r="Y3">
-        <v>-0.114403436347067</v>
+        <v>-0.03859225458811992</v>
       </c>
       <c r="Z3">
-        <v>0.5236768802228413</v>
+        <v>0.7247023809523812</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1059239785773406</v>
+        <v>0.07724362736925268</v>
       </c>
       <c r="AC3">
-        <v>-0.1059239785773406</v>
+        <v>-0.07724362736925268</v>
       </c>
       <c r="AD3">
-        <v>12.1</v>
+        <v>11</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>12.1</v>
+        <v>11</v>
       </c>
       <c r="AG3">
-        <v>-10.4</v>
+        <v>-15.8</v>
       </c>
       <c r="AH3">
-        <v>0.2929782082324455</v>
+        <v>0.2576112412177986</v>
       </c>
       <c r="AI3">
-        <v>0.1006655574043261</v>
+        <v>0.08613938919342208</v>
       </c>
       <c r="AJ3">
-        <v>-0.5531914893617023</v>
+        <v>-0.9937106918238995</v>
       </c>
       <c r="AK3">
-        <v>-0.1064483111566019</v>
+        <v>-0.1565906838453915</v>
       </c>
       <c r="AL3">
         <v>0</v>
